--- a/data/trans_dic/IP12B$otros-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor</t>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 37,35</t>
+          <t>6,32; 36,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,04</t>
+          <t>0,0; 27,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,84</t>
+          <t>0,0; 42,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,85</t>
+          <t>0,0; 26,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,12</t>
+          <t>0,0; 24,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 23,68</t>
+          <t>5,66; 24,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,56</t>
+          <t>0,0; 17,04</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,24</t>
+          <t>0,0; 21,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 26,66</t>
+          <t>3,0; 27,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 30,09</t>
+          <t>5,5; 29,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 33,35</t>
+          <t>6,64; 34,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,63</t>
+          <t>0,0; 13,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 38,07</t>
+          <t>6,81; 34,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 23,0</t>
+          <t>4,54; 23,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 16,27</t>
+          <t>1,98; 15,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 27,29</t>
+          <t>8,17; 26,81</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,94</t>
+          <t>0,0; 32,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,68</t>
+          <t>0,0; 33,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 43,05</t>
+          <t>0,0; 41,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,81</t>
+          <t>0,0; 45,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,93</t>
+          <t>0,0; 34,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,45</t>
+          <t>0,0; 33,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 25,66</t>
+          <t>2,55; 24,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 24,01</t>
+          <t>2,79; 25,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 30,03</t>
+          <t>5,51; 27,99</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 56,72</t>
+          <t>7,25; 56,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,4</t>
+          <t>0,0; 38,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,37</t>
+          <t>0,0; 42,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 67,72</t>
+          <t>8,85; 67,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 40,59</t>
+          <t>8,33; 43,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,23</t>
+          <t>0,0; 51,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 49,81</t>
+          <t>12,53; 50,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 35,54</t>
+          <t>7,92; 33,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,52</t>
+          <t>0,0; 31,01</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 17,89</t>
+          <t>3,06; 17,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 22,26</t>
+          <t>7,37; 22,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 22,1</t>
+          <t>7,02; 23,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 27,83</t>
+          <t>10,1; 26,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,43</t>
+          <t>3,88; 15,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 20,65</t>
+          <t>5,61; 21,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,26</t>
+          <t>8,17; 19,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,03</t>
+          <t>7,11; 16,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 18,67</t>
+          <t>8,04; 18,16</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1136; 6612</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3318</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3994</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3500</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4442</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1767; 7768</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3282</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2951</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6574</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3418</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>608; 5587</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1250; 6783</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1302; 6831</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3461</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1243; 6368</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1618; 8460</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>900; 7161</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3347; 10984</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2208</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3675</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3442</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4751</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4977</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4530</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3497</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4754</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>528; 5068</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>676; 6126</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1436; 7297</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2652</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>576; 4477</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3456</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3618</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>690; 5236</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1248; 6494</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4175</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1972; 7884</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1906; 8027</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5173</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11878</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>13589</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>12830</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1344; 7551</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4517; 13485</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3871; 12972</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4716; 12604</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2467; 9817</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2686; 10056</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7404; 17859</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>8877; 20553</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8280; 18700</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$otros-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,22 +683,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 36,81</t>
+          <t>6,81; 35,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,96</t>
+          <t>0,0; 28,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,84</t>
+          <t>0,0; 36,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,45</t>
+          <t>0,0; 23,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,07</t>
+          <t>0,0; 20,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 24,9</t>
+          <t>4,59; 25,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,04</t>
+          <t>0,0; 17,21</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,28</t>
+          <t>0,0; 23,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 27,6</t>
+          <t>3,13; 29,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 29,85</t>
+          <t>5,32; 29,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 34,81</t>
+          <t>6,54; 35,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,78</t>
+          <t>0,0; 15,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 34,9</t>
+          <t>6,92; 37,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 23,71</t>
+          <t>5,2; 23,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 15,79</t>
+          <t>1,61; 15,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 26,81</t>
+          <t>8,23; 26,78</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,04</t>
+          <t>0,0; 40,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,91</t>
+          <t>0,0; 34,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,38</t>
+          <t>5,22; 49,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,45</t>
+          <t>0,0; 35,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,21</t>
+          <t>0,0; 35,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,85</t>
+          <t>0,0; 31,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 24,47</t>
+          <t>2,57; 27,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,28</t>
+          <t>2,77; 24,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 27,99</t>
+          <t>5,32; 29,0</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 56,36</t>
+          <t>0,0; 56,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,08</t>
+          <t>0,0; 40,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,52</t>
+          <t>0,0; 46,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 67,19</t>
+          <t>8,73; 59,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 43,33</t>
+          <t>8,11; 43,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,1</t>
+          <t>0,0; 34,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 50,1</t>
+          <t>12,45; 49,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 33,36</t>
+          <t>7,71; 34,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,01</t>
+          <t>0,0; 27,55</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 17,21</t>
+          <t>3,14; 17,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,0</t>
+          <t>6,94; 21,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 23,53</t>
+          <t>7,77; 22,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,1; 26,98</t>
+          <t>9,46; 28,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 15,44</t>
+          <t>3,64; 15,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 21,01</t>
+          <t>5,23; 20,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 19,71</t>
+          <t>8,52; 19,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,46</t>
+          <t>7,0; 16,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,16</t>
+          <t>7,74; 18,01</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1136; 6612</t>
+          <t>1223; 6415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3318</t>
+          <t>0; 3357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3994</t>
+          <t>0; 3418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3500</t>
+          <t>0; 3159</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4442</t>
+          <t>0; 3853</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1767; 7768</t>
+          <t>1431; 8055</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3282</t>
+          <t>0; 3315</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3418</t>
+          <t>0; 3728</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>608; 5587</t>
+          <t>633; 6060</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1250; 6783</t>
+          <t>1209; 6797</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1302; 6831</t>
+          <t>1283; 6900</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1243; 6368</t>
+          <t>1262; 6903</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1618; 8460</t>
+          <t>1855; 8224</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>900; 7161</t>
+          <t>731; 6809</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3347; 10984</t>
+          <t>3370; 10972</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3442</t>
+          <t>0; 4305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4751</t>
+          <t>0; 4802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4977</t>
+          <t>628; 5900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>0; 3572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3497</t>
+          <t>0; 3665</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4754</t>
+          <t>0; 4411</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>528; 5068</t>
+          <t>532; 5634</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>676; 6126</t>
+          <t>672; 5838</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1436; 7297</t>
+          <t>1388; 7561</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>576; 4477</t>
+          <t>0; 4499</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3456</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3618</t>
+          <t>0; 3918</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>690; 5236</t>
+          <t>680; 4655</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1248; 6494</t>
+          <t>1215; 6532</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4175</t>
+          <t>0; 2839</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1972; 7884</t>
+          <t>1960; 7836</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1906; 8027</t>
+          <t>1855; 8254</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5173</t>
+          <t>0; 4595</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1344; 7551</t>
+          <t>1378; 7814</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4517; 13485</t>
+          <t>4255; 13414</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3871; 12972</t>
+          <t>4281; 12226</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4716; 12604</t>
+          <t>4420; 13198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2467; 9817</t>
+          <t>2311; 9887</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2686; 10056</t>
+          <t>2505; 9701</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7404; 17859</t>
+          <t>7715; 17813</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8877; 20553</t>
+          <t>8735; 20341</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8280; 18700</t>
+          <t>7974; 18549</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$otros-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>17,85%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,03%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 37,84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 27,85</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6,81; 35,71</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,29</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,87</t>
+          <t>6,71; 37,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,88</t>
+          <t>0,0; 21,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 25,82</t>
+          <t>4,18; 23,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,21</t>
+          <t>0,0; 17,56</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,9%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>14,29%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,22</t>
+          <t>6,4; 33,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 29,94</t>
+          <t>0,0; 16,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 29,92</t>
+          <t>6,83; 38,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 35,16</t>
+          <t>0,0; 21,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,38</t>
+          <t>3,1; 26,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 37,83</t>
+          <t>5,39; 30,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 23,05</t>
+          <t>5,15; 23,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 15,01</t>
+          <t>2,01; 16,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 26,78</t>
+          <t>8,19; 27,29</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,79%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>11,29%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18,36%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,07</t>
+          <t>0,0; 31,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,27</t>
+          <t>0,0; 33,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 49,05</t>
+          <t>0,0; 32,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,84</t>
+          <t>0,0; 29,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,85</t>
+          <t>0,0; 38,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,41</t>
+          <t>4,98; 43,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 27,2</t>
+          <t>2,53; 25,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 24,09</t>
+          <t>2,76; 24,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 29,0</t>
+          <t>5,48; 30,03</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,48%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,28%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,03%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,63</t>
+          <t>8,71; 67,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,17</t>
+          <t>8,11; 40,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,05</t>
+          <t>0,0; 34,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 59,73</t>
+          <t>7,5; 56,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 43,59</t>
+          <t>0,0; 44,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,75</t>
+          <t>0,0; 48,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,45; 49,79</t>
+          <t>12,37; 49,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 34,3</t>
+          <t>7,93; 35,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,55</t>
+          <t>0,0; 28,52</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,54%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,43%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 17,81</t>
+          <t>10,09; 27,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,89</t>
+          <t>4,05; 15,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 22,18</t>
+          <t>5,4; 20,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 28,26</t>
+          <t>4,07; 17,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,56</t>
+          <t>7,5; 22,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 20,27</t>
+          <t>7,56; 22,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 19,67</t>
+          <t>8,27; 19,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,0; 16,29</t>
+          <t>6,88; 16,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 18,01</t>
+          <t>7,72; 18,67</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>3207</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1072</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3528</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3685</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1223; 6415</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3357</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3418</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3159</t>
+          <t>1205; 6709</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3853</t>
+          <t>0; 3898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1431; 8055</t>
+          <t>1306; 7388</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3315</t>
+          <t>0; 3382</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>707</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2206</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3246</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3327</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3728</t>
+          <t>1256; 6545</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>633; 6060</t>
+          <t>0; 4177</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1209; 6797</t>
+          <t>1247; 6947</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1283; 6900</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>627; 5396</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1262; 6903</t>
+          <t>1224; 6838</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1855; 8224</t>
+          <t>1838; 8205</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>731; 6809</t>
+          <t>913; 7382</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3370; 10972</t>
+          <t>3354; 11181</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1159</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1582</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2208</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4305</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4802</t>
+          <t>0; 3468</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>628; 5900</t>
+          <t>0; 4558</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3572</t>
+          <t>0; 3217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3665</t>
+          <t>0; 5420</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4411</t>
+          <t>599; 5178</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>532; 5634</t>
+          <t>525; 5315</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>672; 5838</t>
+          <t>668; 5817</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1388; 7561</t>
+          <t>1430; 7828</t>
         </is>
       </c>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2652</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1906</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>874</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2652</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3219</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4499</t>
+          <t>679; 5278</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>1216; 6083</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3918</t>
+          <t>0; 2796</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>680; 4655</t>
+          <t>596; 4506</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1215; 6532</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2839</t>
+          <t>0; 4116</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1960; 7836</t>
+          <t>1947; 7839</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1855; 8254</t>
+          <t>1909; 8552</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 4757</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3772</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>8301</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>7401</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8106</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5429</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1378; 7814</t>
+          <t>4714; 12997</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4255; 13414</t>
+          <t>2571; 9810</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4281; 12226</t>
+          <t>2585; 9882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4420; 13198</t>
+          <t>1786; 7849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2311; 9887</t>
+          <t>4596; 13643</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2505; 9701</t>
+          <t>4168; 12183</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7715; 17813</t>
+          <t>7496; 17444</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8735; 20341</t>
+          <t>8587; 20013</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7974; 18549</t>
+          <t>7951; 19226</t>
         </is>
       </c>
     </row>
